--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Butterflies/Large-White-Butterfly.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Butterflies/Large-White-Butterfly.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
